--- a/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_21_7.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_21_7.xlsx
@@ -513,1376 +513,1376 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_21_7_0</t>
+          <t>model_21_7_1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9999116908631527</v>
+        <v>0.9996137597179973</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6658926753628788</v>
+        <v>0.7012302137123321</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9993890018971062</v>
+        <v>0.9985259405293345</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999521405045876</v>
+        <v>0.9981624199269985</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9996388448012868</v>
+        <v>0.9986501185117294</v>
       </c>
       <c r="G2" t="n">
-        <v>5.242411838865212e-05</v>
+        <v>0.000229288916108221</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1983405405895215</v>
+        <v>0.177362651323113</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002338535155382586</v>
+        <v>0.0007328616067433615</v>
       </c>
       <c r="J2" t="n">
-        <v>1.441268823611894e-05</v>
+        <v>0.0007001941178401371</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001241316492630939</v>
+        <v>0.0007165257796703407</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003845471184798424</v>
+        <v>0.004977979309486937</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007240450150967971</v>
+        <v>0.01514228899830607</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000060554836695</v>
+        <v>1.000264850479088</v>
       </c>
       <c r="O2" t="n">
-        <v>0.007548691103692725</v>
+        <v>0.01578692758982339</v>
       </c>
       <c r="P2" t="n">
-        <v>137.7122875958771</v>
+        <v>134.7610554144361</v>
       </c>
       <c r="Q2" t="n">
-        <v>209.6259612631009</v>
+        <v>206.6747290816599</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_21_7_1</t>
+          <t>model_21_7_2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9998861785255796</v>
+        <v>0.9996137597179973</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6650250325604359</v>
+        <v>0.7012302137123321</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9991160314696023</v>
+        <v>0.9985259405293345</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999344969097979</v>
+        <v>0.9981624199269985</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9994791247261767</v>
+        <v>0.9986501185117294</v>
       </c>
       <c r="G3" t="n">
-        <v>6.756934404760123e-05</v>
+        <v>0.000229288916108221</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1988556108372692</v>
+        <v>0.177362651323113</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0003383302623685203</v>
+        <v>0.0007328616067433615</v>
       </c>
       <c r="J3" t="n">
-        <v>1.97259835159369e-05</v>
+        <v>0.0007001941178401371</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0001790285922241603</v>
+        <v>0.0007165257796703407</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004092896466710265</v>
+        <v>0.004977979309486937</v>
       </c>
       <c r="M3" t="n">
-        <v>0.00822005742361945</v>
+        <v>0.01514228899830607</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000078049011031</v>
+        <v>1.000264850479088</v>
       </c>
       <c r="O3" t="n">
-        <v>0.008570002286007586</v>
+        <v>0.01578692758982339</v>
       </c>
       <c r="P3" t="n">
-        <v>137.2047123363867</v>
+        <v>134.7610554144361</v>
       </c>
       <c r="Q3" t="n">
-        <v>209.1183860036105</v>
+        <v>206.6747290816599</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_21_7_2</t>
+          <t>model_21_7_12</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9998573794650228</v>
+        <v>0.9996137597179973</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6642399898815627</v>
+        <v>0.7012302109199942</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9988241655973246</v>
+        <v>0.9985259405293345</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9999099612580166</v>
+        <v>0.9981624199269985</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9993058759931266</v>
+        <v>0.9986501185117294</v>
       </c>
       <c r="G4" t="n">
-        <v>8.466571044878062e-05</v>
+        <v>0.000229288916108221</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1993216460835262</v>
+        <v>0.1773626529807654</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0004500390548746194</v>
+        <v>0.0007328616067433615</v>
       </c>
       <c r="J4" t="n">
-        <v>2.711479312929165e-05</v>
+        <v>0.0007001941178401371</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0002385754325933146</v>
+        <v>0.0007165257796703407</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004318731855420877</v>
+        <v>0.004977979309486937</v>
       </c>
       <c r="M4" t="n">
-        <v>0.009201397200902732</v>
+        <v>0.01514228899830607</v>
       </c>
       <c r="N4" t="n">
-        <v>1.00009779693827</v>
+        <v>1.000264850479088</v>
       </c>
       <c r="O4" t="n">
-        <v>0.009593119729263204</v>
+        <v>0.01578692758982339</v>
       </c>
       <c r="P4" t="n">
-        <v>136.7535997471793</v>
+        <v>134.7610554144361</v>
       </c>
       <c r="Q4" t="n">
-        <v>208.6672734144032</v>
+        <v>206.6747290816599</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_21_7_3</t>
+          <t>model_21_7_22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9998269950827157</v>
+        <v>0.9996137597179973</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6635389158081324</v>
+        <v>0.7012302109199942</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9985262365923325</v>
+        <v>0.9985259405293345</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9998813799590883</v>
+        <v>0.9981624199269985</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9991274690349203</v>
+        <v>0.9986501185117294</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001027031923232561</v>
+        <v>0.000229288916108221</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1997378339383375</v>
+        <v>0.1773626529807654</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00056406845180437</v>
+        <v>0.0007328616067433615</v>
       </c>
       <c r="J5" t="n">
-        <v>3.572193257545138e-05</v>
+        <v>0.0007001941178401371</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0002998951921899107</v>
+        <v>0.0007165257796703407</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004591413601839215</v>
+        <v>0.004977979309486937</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01013425835092317</v>
+        <v>0.01514228899830607</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000118631943281</v>
+        <v>1.000264850479088</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01056569470972881</v>
+        <v>0.01578692758982339</v>
       </c>
       <c r="P5" t="n">
-        <v>136.3673347150947</v>
+        <v>134.7610554144361</v>
       </c>
       <c r="Q5" t="n">
-        <v>208.2810083823186</v>
+        <v>206.6747290816599</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_21_7_4</t>
+          <t>model_21_7_21</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9997959542650942</v>
+        <v>0.9996137597179973</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6629093996802921</v>
+        <v>0.7012302109199942</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9982286764806978</v>
+        <v>0.9985259405293345</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9998504987987189</v>
+        <v>0.9981624199269985</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9989482716597359</v>
+        <v>0.9986501185117294</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001211303625569287</v>
+        <v>0.000229288916108221</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2001115419055043</v>
+        <v>0.1773626529807654</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0006779566584292253</v>
+        <v>0.0007328616067433615</v>
       </c>
       <c r="J6" t="n">
-        <v>4.502166574102175e-05</v>
+        <v>0.0007001941178401371</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0003614866238085718</v>
+        <v>0.0007165257796703407</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00489989052551777</v>
+        <v>0.004977979309486937</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01100592397561098</v>
+        <v>0.01514228899830607</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000139917075364</v>
+        <v>1.000264850479088</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01147446894465618</v>
+        <v>0.01578692758982339</v>
       </c>
       <c r="P6" t="n">
-        <v>136.0372864316351</v>
+        <v>134.7610554144361</v>
       </c>
       <c r="Q6" t="n">
-        <v>207.9509600988589</v>
+        <v>206.6747290816599</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_21_7_5</t>
+          <t>model_21_7_20</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9997649708907359</v>
+        <v>0.9996137597179973</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6623422817669664</v>
+        <v>0.7012302109199942</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9979365990367779</v>
+        <v>0.9985259405293345</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9998184364341903</v>
+        <v>0.9981624199269985</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9987715889825153</v>
+        <v>0.9986501185117294</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001395234319880605</v>
+        <v>0.000229288916108221</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2004482075970726</v>
+        <v>0.1773626529807654</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007897464279008675</v>
+        <v>0.0007328616067433615</v>
       </c>
       <c r="J7" t="n">
-        <v>5.467711363241976e-05</v>
+        <v>0.0007001941178401371</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0004222137355814878</v>
+        <v>0.0007165257796703407</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005176531704698672</v>
+        <v>0.004977979309486937</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01181200372451941</v>
+        <v>0.01514228899830607</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000161162817781</v>
+        <v>1.000264850479088</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01231486517729075</v>
+        <v>0.01578692758982339</v>
       </c>
       <c r="P7" t="n">
-        <v>135.7545559991357</v>
+        <v>134.7610554144361</v>
       </c>
       <c r="Q7" t="n">
-        <v>207.6682296663596</v>
+        <v>206.6747290816599</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_21_7_6</t>
+          <t>model_21_7_19</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9997347236870319</v>
+        <v>0.9996137597179973</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6618339460488014</v>
+        <v>0.7012302109199942</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9976548932911292</v>
+        <v>0.9985259405293345</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9997863647292868</v>
+        <v>0.9981624199269985</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9986006982621455</v>
+        <v>0.9986501185117294</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001574794787179522</v>
+        <v>0.000229288916108221</v>
       </c>
       <c r="H8" t="n">
-        <v>0.200749977638335</v>
+        <v>0.1773626529807654</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0008975665318508727</v>
+        <v>0.0007328616067433615</v>
       </c>
       <c r="J8" t="n">
-        <v>6.433537433894793e-05</v>
+        <v>0.0007001941178401371</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0004809501099680237</v>
+        <v>0.0007165257796703407</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005423628390013023</v>
+        <v>0.004977979309486937</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01254908278393095</v>
+        <v>0.01514228899830607</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000181903757464</v>
+        <v>1.000264850479088</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01308332321822544</v>
+        <v>0.01578692758982339</v>
       </c>
       <c r="P8" t="n">
-        <v>135.5124308040837</v>
+        <v>134.7610554144361</v>
       </c>
       <c r="Q8" t="n">
-        <v>207.4261044713075</v>
+        <v>206.6747290816599</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_21_7_7</t>
+          <t>model_21_7_18</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9993673255948204</v>
+        <v>0.9996137597179973</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6573581823667294</v>
+        <v>0.7012302109199942</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9943598947494264</v>
+        <v>0.9985259405293345</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9993734003993948</v>
+        <v>0.9981624199269985</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9965851856558733</v>
+        <v>0.9986501185117294</v>
       </c>
       <c r="G9" t="n">
-        <v>0.000375582857025843</v>
+        <v>0.000229288916108221</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2034069843029369</v>
+        <v>0.1773626529807654</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002158694821809974</v>
+        <v>0.0007328616067433615</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001886978668409228</v>
+        <v>0.0007001941178401371</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001173696344325448</v>
+        <v>0.0007165257796703407</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0075617436313138</v>
+        <v>0.004977979309486937</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01937996019154433</v>
+        <v>0.01514228899830607</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000433833877837</v>
+        <v>1.000264850479088</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0202050052189465</v>
+        <v>0.01578692758982339</v>
       </c>
       <c r="P9" t="n">
-        <v>133.774062906486</v>
+        <v>134.7610554144361</v>
       </c>
       <c r="Q9" t="n">
-        <v>205.6877365737099</v>
+        <v>206.6747290816599</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_21_7_8</t>
+          <t>model_21_7_17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9993672065994504</v>
+        <v>0.9996137597179973</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6573570588011013</v>
+        <v>0.7012302109199942</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9943588520331903</v>
+        <v>0.9985259405293345</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9993732594438338</v>
+        <v>0.9981624199269985</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9965845433394744</v>
+        <v>0.9986501185117294</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0003756534978177951</v>
+        <v>0.000229288916108221</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2034076513000292</v>
+        <v>0.1773626529807654</v>
       </c>
       <c r="I10" t="n">
-        <v>0.002159093911195663</v>
+        <v>0.0007328616067433615</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0001887403150226146</v>
+        <v>0.0007001941178401371</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001173917113109139</v>
+        <v>0.0007165257796703407</v>
       </c>
       <c r="L10" t="n">
-        <v>0.007562257481386928</v>
+        <v>0.004977979309486937</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01938178262745187</v>
+        <v>0.01514228899830607</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000433915474663</v>
+        <v>1.000264850479088</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02020690523972359</v>
+        <v>0.01578692758982339</v>
       </c>
       <c r="P10" t="n">
-        <v>133.7736867756361</v>
+        <v>134.7610554144361</v>
       </c>
       <c r="Q10" t="n">
-        <v>205.6873604428599</v>
+        <v>206.6747290816599</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_21_7_9</t>
+          <t>model_21_7_16</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9993670899618228</v>
+        <v>0.9996137597179973</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6573560075849554</v>
+        <v>0.7012302109199942</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9943578271007605</v>
+        <v>0.9985259405293345</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9993731249556659</v>
+        <v>0.9981624199269985</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9965839137580503</v>
+        <v>0.9986501185117294</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0003757227389520612</v>
+        <v>0.000229288916108221</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2034082753473436</v>
+        <v>0.1773626529807654</v>
       </c>
       <c r="I11" t="n">
-        <v>0.002159486194004356</v>
+        <v>0.0007328616067433615</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001887808155757246</v>
+        <v>0.0007001941178401371</v>
       </c>
       <c r="K11" t="n">
-        <v>0.00117413350479004</v>
+        <v>0.0007165257796703407</v>
       </c>
       <c r="L11" t="n">
-        <v>0.007562868908699694</v>
+        <v>0.004977979309486937</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01938356878781772</v>
+        <v>0.01514228899830607</v>
       </c>
       <c r="N11" t="n">
-        <v>1.00043399545475</v>
+        <v>1.000264850479088</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02020876744063407</v>
+        <v>0.01578692758982339</v>
       </c>
       <c r="P11" t="n">
-        <v>133.7733181659779</v>
+        <v>134.7610554144361</v>
       </c>
       <c r="Q11" t="n">
-        <v>205.6869918332017</v>
+        <v>206.6747290816599</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_21_7_10</t>
+          <t>model_21_7_15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9993669947769371</v>
+        <v>0.9996137597179973</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6573550391332268</v>
+        <v>0.7012302109199942</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9943569711178097</v>
+        <v>0.9985259405293345</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9993730400806689</v>
+        <v>0.9981624199269985</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9965834133841762</v>
+        <v>0.9986501185117294</v>
       </c>
       <c r="G12" t="n">
-        <v>0.000375779244811951</v>
+        <v>0.000229288916108221</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2034088502621246</v>
+        <v>0.1773626529807654</v>
       </c>
       <c r="I12" t="n">
-        <v>0.002159813813061286</v>
+        <v>0.0007328616067433615</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0001888063753285197</v>
+        <v>0.0007001941178401371</v>
       </c>
       <c r="K12" t="n">
-        <v>0.00117430548690317</v>
+        <v>0.0007165257796703407</v>
       </c>
       <c r="L12" t="n">
-        <v>0.007563300491996108</v>
+        <v>0.004977979309486937</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01938502630413358</v>
+        <v>0.01514228899830607</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000434060724386</v>
+        <v>1.000264850479088</v>
       </c>
       <c r="O12" t="n">
-        <v>0.02021028700643698</v>
+        <v>0.01578692758982339</v>
       </c>
       <c r="P12" t="n">
-        <v>133.7730174037113</v>
+        <v>134.7610554144361</v>
       </c>
       <c r="Q12" t="n">
-        <v>205.6866910709351</v>
+        <v>206.6747290816599</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_21_7_11</t>
+          <t>model_21_7_14</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9993668913542753</v>
+        <v>0.9996137597179973</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6573539695098944</v>
+        <v>0.7012302109199942</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9943560916976472</v>
+        <v>0.9985259405293345</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9993728834867687</v>
+        <v>0.9981624199269985</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9965828510807452</v>
+        <v>0.9986501185117294</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0003758406409716622</v>
+        <v>0.000229288916108221</v>
       </c>
       <c r="H13" t="n">
-        <v>0.20340948523674</v>
+        <v>0.1773626529807654</v>
       </c>
       <c r="I13" t="n">
-        <v>0.002160150402480614</v>
+        <v>0.0007328616067433615</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0001888535329310578</v>
+        <v>0.0007001941178401371</v>
       </c>
       <c r="K13" t="n">
-        <v>0.001174498754652146</v>
+        <v>0.0007165257796703407</v>
       </c>
       <c r="L13" t="n">
-        <v>0.007563788372747727</v>
+        <v>0.004977979309486937</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01938660983698961</v>
+        <v>0.01514228899830607</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000434131642783</v>
+        <v>1.000264850479088</v>
       </c>
       <c r="O13" t="n">
-        <v>0.02021193795356505</v>
+        <v>0.01578692758982339</v>
       </c>
       <c r="P13" t="n">
-        <v>133.7726906632351</v>
+        <v>134.7610554144361</v>
       </c>
       <c r="Q13" t="n">
-        <v>205.6863643304589</v>
+        <v>206.6747290816599</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>model_21_7_12</t>
+          <t>model_21_7_13</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9993668154230414</v>
+        <v>0.9996137597179973</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6573531568234089</v>
+        <v>0.7012302109199942</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9943554190350572</v>
+        <v>0.9985259405293345</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9993728028537421</v>
+        <v>0.9981624199269985</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9965824452884122</v>
+        <v>0.9986501185117294</v>
       </c>
       <c r="G14" t="n">
-        <v>0.000375885717032156</v>
+        <v>0.000229288916108221</v>
       </c>
       <c r="H14" t="n">
-        <v>0.203409967682544</v>
+        <v>0.1773626529807654</v>
       </c>
       <c r="I14" t="n">
-        <v>0.002160407857472166</v>
+        <v>0.0007328616067433615</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0001888778152320777</v>
+        <v>0.0007001941178401371</v>
       </c>
       <c r="K14" t="n">
-        <v>0.001174638228406689</v>
+        <v>0.0007165257796703407</v>
       </c>
       <c r="L14" t="n">
-        <v>0.007564138593446868</v>
+        <v>0.004977979309486937</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01938777235868412</v>
+        <v>0.01514228899830607</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000434183709914</v>
+        <v>1.000264850479088</v>
       </c>
       <c r="O14" t="n">
-        <v>0.02021314996621485</v>
+        <v>0.01578692758982339</v>
       </c>
       <c r="P14" t="n">
-        <v>133.7724508096763</v>
+        <v>134.7610554144361</v>
       </c>
       <c r="Q14" t="n">
-        <v>205.6861244769001</v>
+        <v>206.6747290816599</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_21_7_13</t>
+          <t>model_21_7_24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9993667272668257</v>
+        <v>0.9996137597179973</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6573523512874344</v>
+        <v>0.7012302109199942</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9943546507535412</v>
+        <v>0.9985259405293345</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9993726931321674</v>
+        <v>0.9981624199269985</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9965819560489328</v>
+        <v>0.9986501185117294</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0003759380503698843</v>
+        <v>0.000229288916108221</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2034104458834958</v>
+        <v>0.1773626529807654</v>
       </c>
       <c r="I15" t="n">
-        <v>0.002160701909667417</v>
+        <v>0.0007328616067433615</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0001889108574285132</v>
+        <v>0.0007001941178401371</v>
       </c>
       <c r="K15" t="n">
-        <v>0.001174806383547965</v>
+        <v>0.0007165257796703407</v>
       </c>
       <c r="L15" t="n">
-        <v>0.00756458621676639</v>
+        <v>0.004977979309486937</v>
       </c>
       <c r="M15" t="n">
-        <v>0.01938912195974548</v>
+        <v>0.01514228899830607</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000434244159891</v>
+        <v>1.000264850479088</v>
       </c>
       <c r="O15" t="n">
-        <v>0.02021455702258745</v>
+        <v>0.01578692758982339</v>
       </c>
       <c r="P15" t="n">
-        <v>133.7721723756066</v>
+        <v>134.7610554144361</v>
       </c>
       <c r="Q15" t="n">
-        <v>205.6858460428304</v>
+        <v>206.6747290816599</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_21_7_14</t>
+          <t>model_21_7_11</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.999366546513311</v>
+        <v>0.9996137597179973</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6573505406185196</v>
+        <v>0.7012302109199942</v>
       </c>
       <c r="D16" t="n">
-        <v>0.994353078875916</v>
+        <v>0.9985259405293345</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9993724638538255</v>
+        <v>0.9981624199269985</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9965809763532435</v>
+        <v>0.9986501185117294</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0003760453534643666</v>
+        <v>0.000229288916108221</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2034115207747805</v>
+        <v>0.1773626529807654</v>
       </c>
       <c r="I16" t="n">
-        <v>0.002161303530371186</v>
+        <v>0.0007328616067433615</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0001889799036487442</v>
+        <v>0.0007001941178401371</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001175143112029605</v>
+        <v>0.0007165257796703407</v>
       </c>
       <c r="L16" t="n">
-        <v>0.007565438254253868</v>
+        <v>0.004977979309486937</v>
       </c>
       <c r="M16" t="n">
-        <v>0.01939188885757049</v>
+        <v>0.01514228899830607</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000434368105158</v>
+        <v>1.000264850479088</v>
       </c>
       <c r="O16" t="n">
-        <v>0.02021744171298114</v>
+        <v>0.01578692758982339</v>
       </c>
       <c r="P16" t="n">
-        <v>133.7716016018653</v>
+        <v>134.7610554144361</v>
       </c>
       <c r="Q16" t="n">
-        <v>205.6852752690891</v>
+        <v>206.6747290816599</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_21_7_15</t>
+          <t>model_21_7_10</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9993665078683419</v>
+        <v>0.9996137597179973</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6573501271989227</v>
+        <v>0.7012302109199942</v>
       </c>
       <c r="D17" t="n">
-        <v>0.994352766816254</v>
+        <v>0.9985259405293345</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9993723843305005</v>
+        <v>0.9981624199269985</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9965807584148729</v>
+        <v>0.9986501185117294</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0003760682947874553</v>
+        <v>0.000229288916108221</v>
       </c>
       <c r="H17" t="n">
-        <v>0.203411766198512</v>
+        <v>0.1773626529807654</v>
       </c>
       <c r="I17" t="n">
-        <v>0.002161422968138137</v>
+        <v>0.0007328616067433615</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0001890038517677474</v>
+        <v>0.0007001941178401371</v>
       </c>
       <c r="K17" t="n">
-        <v>0.001175218019021032</v>
+        <v>0.0007165257796703407</v>
       </c>
       <c r="L17" t="n">
-        <v>0.007565668265112671</v>
+        <v>0.004977979309486937</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0193924803670767</v>
+        <v>0.01514228899830607</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000434394604566</v>
+        <v>1.000264850479088</v>
       </c>
       <c r="O17" t="n">
-        <v>0.02021805840427162</v>
+        <v>0.01578692758982339</v>
       </c>
       <c r="P17" t="n">
-        <v>133.77147959199</v>
+        <v>134.7610554144361</v>
       </c>
       <c r="Q17" t="n">
-        <v>205.6851532592138</v>
+        <v>206.6747290816599</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_21_7_16</t>
+          <t>model_21_7_9</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9993664212899309</v>
+        <v>0.9996137597179973</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6573492111487107</v>
+        <v>0.7012302109199942</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9943519746720164</v>
+        <v>0.9985259405293345</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9993723243983551</v>
+        <v>0.9981624199269985</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9965803085767556</v>
+        <v>0.9986501185117294</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0003761196914722247</v>
+        <v>0.000229288916108221</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2034123100054891</v>
+        <v>0.1773626529807654</v>
       </c>
       <c r="I18" t="n">
-        <v>0.002161726153555348</v>
+        <v>0.0007328616067433615</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0001890219000843509</v>
+        <v>0.0007001941178401371</v>
       </c>
       <c r="K18" t="n">
-        <v>0.001175372631629679</v>
+        <v>0.0007165257796703407</v>
       </c>
       <c r="L18" t="n">
-        <v>0.007566118283239859</v>
+        <v>0.004977979309486937</v>
       </c>
       <c r="M18" t="n">
-        <v>0.01939380549227574</v>
+        <v>0.01514228899830607</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000434453972619</v>
+        <v>1.000264850479088</v>
       </c>
       <c r="O18" t="n">
-        <v>0.02021943994279377</v>
+        <v>0.01578692758982339</v>
       </c>
       <c r="P18" t="n">
-        <v>133.7712062736931</v>
+        <v>134.7610554144361</v>
       </c>
       <c r="Q18" t="n">
-        <v>205.6848799409169</v>
+        <v>206.6747290816599</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_21_7_17</t>
+          <t>model_21_7_8</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9993661850485761</v>
+        <v>0.9996137597179973</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6573471348980997</v>
+        <v>0.7012302109199942</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9943498788697089</v>
+        <v>0.9985259405293345</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9993720773820057</v>
+        <v>0.9981624199269985</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9965790293978484</v>
+        <v>0.9986501185117294</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0003762599345455114</v>
+        <v>0.000229288916108221</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2034135425575412</v>
+        <v>0.1773626529807654</v>
       </c>
       <c r="I19" t="n">
-        <v>0.002162528301279171</v>
+        <v>0.0007328616067433615</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0001890962880318726</v>
+        <v>0.0007001941178401371</v>
       </c>
       <c r="K19" t="n">
-        <v>0.001175812294655522</v>
+        <v>0.0007165257796703407</v>
       </c>
       <c r="L19" t="n">
-        <v>0.007567025135791975</v>
+        <v>0.004977979309486937</v>
       </c>
       <c r="M19" t="n">
-        <v>0.01939742082199361</v>
+        <v>0.01514228899830607</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000434615966691</v>
+        <v>1.000264850479088</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0202232091845825</v>
+        <v>0.01578692758982339</v>
       </c>
       <c r="P19" t="n">
-        <v>133.7704606762842</v>
+        <v>134.7610554144361</v>
       </c>
       <c r="Q19" t="n">
-        <v>205.684134343508</v>
+        <v>206.6747290816599</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_21_7_18</t>
+          <t>model_21_7_7</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9993661851805767</v>
+        <v>0.9996137597179973</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6573470917460602</v>
+        <v>0.7012302109199942</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9943498746412769</v>
+        <v>0.9985259405293345</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9993720843825482</v>
+        <v>0.9981624199269985</v>
       </c>
       <c r="F20" t="n">
-        <v>0.996579030110364</v>
+        <v>0.9986501185117294</v>
       </c>
       <c r="G20" t="n">
-        <v>0.000376259856184193</v>
+        <v>0.000229288916108221</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2034135681744559</v>
+        <v>0.1773626529807654</v>
       </c>
       <c r="I20" t="n">
-        <v>0.002162529919669946</v>
+        <v>0.0007328616067433615</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0001890941798475751</v>
+        <v>0.0007001941178401371</v>
       </c>
       <c r="K20" t="n">
-        <v>0.001175812049758761</v>
+        <v>0.0007165257796703407</v>
       </c>
       <c r="L20" t="n">
-        <v>0.007567016193838989</v>
+        <v>0.004977979309486937</v>
       </c>
       <c r="M20" t="n">
-        <v>0.01939741880210336</v>
+        <v>0.01514228899830607</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000434615876176</v>
+        <v>1.000264850479088</v>
       </c>
       <c r="O20" t="n">
-        <v>0.02022320707870134</v>
+        <v>0.01578692758982339</v>
       </c>
       <c r="P20" t="n">
-        <v>133.7704610928118</v>
+        <v>134.7610554144361</v>
       </c>
       <c r="Q20" t="n">
-        <v>205.6841347600356</v>
+        <v>206.6747290816599</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_21_7_19</t>
+          <t>model_21_7_6</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9993661799954504</v>
+        <v>0.9996137597179973</v>
       </c>
       <c r="C21" t="n">
-        <v>0.657347062096681</v>
+        <v>0.7012302109199942</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9943498287123793</v>
+        <v>0.9985259405293345</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9993720788702335</v>
+        <v>0.9981624199269985</v>
       </c>
       <c r="F21" t="n">
-        <v>0.996579002123107</v>
+        <v>0.9986501185117294</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0003762629342992218</v>
+        <v>0.000229288916108221</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2034135857756081</v>
+        <v>0.1773626529807654</v>
       </c>
       <c r="I21" t="n">
-        <v>0.002162547498503851</v>
+        <v>0.0007328616067433615</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0001890958398582655</v>
+        <v>0.0007001941178401371</v>
       </c>
       <c r="K21" t="n">
-        <v>0.001175821669181058</v>
+        <v>0.0007165257796703407</v>
       </c>
       <c r="L21" t="n">
-        <v>0.007567005070280887</v>
+        <v>0.004977979309486937</v>
       </c>
       <c r="M21" t="n">
-        <v>0.01939749814535941</v>
+        <v>0.01514228899830607</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000434619431691</v>
+        <v>1.000264850479088</v>
       </c>
       <c r="O21" t="n">
-        <v>0.02022328979976406</v>
+        <v>0.01578692758982339</v>
       </c>
       <c r="P21" t="n">
-        <v>133.7704447312341</v>
+        <v>134.7610554144361</v>
       </c>
       <c r="Q21" t="n">
-        <v>205.6841183984579</v>
+        <v>206.6747290816599</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_21_7_24</t>
+          <t>model_21_7_5</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9993661682967946</v>
+        <v>0.9996137597179973</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6573469353960679</v>
+        <v>0.7012302109199942</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9943497114594422</v>
+        <v>0.9985259405293345</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9993720837574944</v>
+        <v>0.9981624199269985</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9965789389797863</v>
+        <v>0.9986501185117294</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0003762698791266403</v>
+        <v>0.000229288916108221</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2034136609905653</v>
+        <v>0.1773626529807654</v>
       </c>
       <c r="I22" t="n">
-        <v>0.002162592375912519</v>
+        <v>0.0007328616067433615</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0001890943680799453</v>
+        <v>0.0007001941178401371</v>
       </c>
       <c r="K22" t="n">
-        <v>0.001175843371996232</v>
+        <v>0.0007165257796703407</v>
       </c>
       <c r="L22" t="n">
-        <v>0.007567004752476268</v>
+        <v>0.004977979309486937</v>
       </c>
       <c r="M22" t="n">
-        <v>0.01939767715801663</v>
+        <v>0.01514228899830607</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000434627453627</v>
+        <v>1.000264850479088</v>
       </c>
       <c r="O22" t="n">
-        <v>0.02022347643336071</v>
+        <v>0.01578692758982339</v>
       </c>
       <c r="P22" t="n">
-        <v>133.7704078168177</v>
+        <v>134.7610554144361</v>
       </c>
       <c r="Q22" t="n">
-        <v>205.6840814840415</v>
+        <v>206.6747290816599</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_21_7_23</t>
+          <t>model_21_7_4</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9993661682967946</v>
+        <v>0.9996137597179973</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6573469335554456</v>
+        <v>0.7012302109199942</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9943497114594422</v>
+        <v>0.9985259405293345</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9993720837574944</v>
+        <v>0.9981624199269985</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9965789389797863</v>
+        <v>0.9986501185117294</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0003762698791266403</v>
+        <v>0.000229288916108221</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2034136620832382</v>
+        <v>0.1773626529807654</v>
       </c>
       <c r="I23" t="n">
-        <v>0.002162592375912519</v>
+        <v>0.0007328616067433615</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0001890943680799453</v>
+        <v>0.0007001941178401371</v>
       </c>
       <c r="K23" t="n">
-        <v>0.001175843371996232</v>
+        <v>0.0007165257796703407</v>
       </c>
       <c r="L23" t="n">
-        <v>0.007567004752476268</v>
+        <v>0.004977979309486937</v>
       </c>
       <c r="M23" t="n">
-        <v>0.01939767715801663</v>
+        <v>0.01514228899830607</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000434627453627</v>
+        <v>1.000264850479088</v>
       </c>
       <c r="O23" t="n">
-        <v>0.02022347643336071</v>
+        <v>0.01578692758982339</v>
       </c>
       <c r="P23" t="n">
-        <v>133.7704078168177</v>
+        <v>134.7610554144361</v>
       </c>
       <c r="Q23" t="n">
-        <v>205.6840814840415</v>
+        <v>206.6747290816599</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_21_7_22</t>
+          <t>model_21_7_3</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9993661681825085</v>
+        <v>0.9996137597179973</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6573469320964735</v>
+        <v>0.7012302109199942</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9943497114594422</v>
+        <v>0.9985259405293345</v>
       </c>
       <c r="E24" t="n">
-        <v>0.999372082349372</v>
+        <v>0.9981624199269985</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9965789383629093</v>
+        <v>0.9986501185117294</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0003762699469718472</v>
+        <v>0.000229288916108221</v>
       </c>
       <c r="H24" t="n">
-        <v>0.203413662949347</v>
+        <v>0.1773626529807654</v>
       </c>
       <c r="I24" t="n">
-        <v>0.002162592375912519</v>
+        <v>0.0007328616067433615</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0001890947921301435</v>
+        <v>0.0007001941178401371</v>
       </c>
       <c r="K24" t="n">
-        <v>0.001175843584021331</v>
+        <v>0.0007165257796703407</v>
       </c>
       <c r="L24" t="n">
-        <v>0.007567007356170849</v>
+        <v>0.004977979309486937</v>
       </c>
       <c r="M24" t="n">
-        <v>0.01939767890681375</v>
+        <v>0.01514228899830607</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000434627531994</v>
+        <v>1.000264850479088</v>
       </c>
       <c r="O24" t="n">
-        <v>0.02022347825660774</v>
+        <v>0.01578692758982339</v>
       </c>
       <c r="P24" t="n">
-        <v>133.7704074561977</v>
+        <v>134.7610554144361</v>
       </c>
       <c r="Q24" t="n">
-        <v>205.6840811234216</v>
+        <v>206.6747290816599</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_21_7_21</t>
+          <t>model_21_7_23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9993661680371343</v>
+        <v>0.9996137597179973</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6573469317152079</v>
+        <v>0.7012302109199942</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9943497100500019</v>
+        <v>0.9985259405293345</v>
       </c>
       <c r="E25" t="n">
-        <v>0.999372082349372</v>
+        <v>0.9981624199269985</v>
       </c>
       <c r="F25" t="n">
-        <v>0.996578937578158</v>
+        <v>0.9986501185117294</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0003762700332722152</v>
+        <v>0.000229288916108221</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2034136631756829</v>
+        <v>0.1773626529807654</v>
       </c>
       <c r="I25" t="n">
-        <v>0.002162592915361899</v>
+        <v>0.0007328616067433615</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0001890947921301435</v>
+        <v>0.0007001941178401371</v>
       </c>
       <c r="K25" t="n">
-        <v>0.001175843853746021</v>
+        <v>0.0007165257796703407</v>
       </c>
       <c r="L25" t="n">
-        <v>0.00756701042624286</v>
+        <v>0.004977979309486937</v>
       </c>
       <c r="M25" t="n">
-        <v>0.01939768113131606</v>
+        <v>0.01514228899830607</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000434627631679</v>
+        <v>1.000264850479088</v>
       </c>
       <c r="O25" t="n">
-        <v>0.02022348057581172</v>
+        <v>0.01578692758982339</v>
       </c>
       <c r="P25" t="n">
-        <v>133.7704069974826</v>
+        <v>134.7610554144361</v>
       </c>
       <c r="Q25" t="n">
-        <v>205.6840806647065</v>
+        <v>206.6747290816599</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_21_7_20</t>
+          <t>model_21_7_0</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9993661680371343</v>
+        <v>0.9996137600588275</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6573469253691706</v>
+        <v>0.701230206053064</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9943497100500019</v>
+        <v>0.9985259345388365</v>
       </c>
       <c r="E26" t="n">
-        <v>0.999372082349372</v>
+        <v>0.9981624310615361</v>
       </c>
       <c r="F26" t="n">
-        <v>0.996578937578158</v>
+        <v>0.9986501140512751</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0003762700332722152</v>
+        <v>0.0002292887137766659</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2034136669429647</v>
+        <v>0.1773626558699854</v>
       </c>
       <c r="I26" t="n">
-        <v>0.002162592915361899</v>
+        <v>0.0007328645850532939</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0001890947921301435</v>
+        <v>0.0007001898751201241</v>
       </c>
       <c r="K26" t="n">
-        <v>0.001175843853746021</v>
+        <v>0.0007165281473081268</v>
       </c>
       <c r="L26" t="n">
-        <v>0.00756701042624286</v>
+        <v>0.004977965407260901</v>
       </c>
       <c r="M26" t="n">
-        <v>0.01939768113131606</v>
+        <v>0.01514228231729503</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000434627631679</v>
+        <v>1.000264850245375</v>
       </c>
       <c r="O26" t="n">
-        <v>0.02022348057581172</v>
+        <v>0.01578692062438789</v>
       </c>
       <c r="P26" t="n">
-        <v>133.7704069974826</v>
+        <v>134.7610571792981</v>
       </c>
       <c r="Q26" t="n">
-        <v>205.6840806647065</v>
+        <v>206.6747308465219</v>
       </c>
     </row>
   </sheetData>
